--- a/results/02_taxa_assemblage/MRT_Method/ModelCompar/tables/confidence_weights.xlsx
+++ b/results/02_taxa_assemblage/MRT_Method/ModelCompar/tables/confidence_weights.xlsx
@@ -452,7 +452,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.207708831576254</v>
+        <v>0.3404407543448494</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.42775575759446</v>
+        <v>2.666310623627961</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -482,11 +482,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8373949349333958</v>
+        <v>0.2096872840624322</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
     </row>
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3888461395970747</v>
+        <v>0.2588983871463814</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -512,11 +512,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.752582670941512</v>
+        <v>1.784950781636385</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
     </row>
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.767945083936907</v>
+        <v>2.981947824886332</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3496409897988013</v>
+        <v>0.7629449302913383</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.757980457734229</v>
+        <v>2.495931550994714</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -572,7 +572,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.191461900257933</v>
+        <v>0.9564671538937354</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.752353028921366</v>
+        <v>3.028073600198286</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.751979366999973</v>
+        <v>2.914708768181651</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -617,11 +617,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.025822252974357</v>
+        <v>0.2826763339785591</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
     </row>
@@ -632,11 +632,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.144221239007055</v>
+        <v>0.1852958794504528</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.181325180777689</v>
+        <v>0.9817373463146232</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.730571954864671</v>
+        <v>2.239244818166248</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -677,11 +677,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8261864634309731</v>
+        <v>0.5326339127680602</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
     </row>
@@ -692,7 +692,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.765959978000378</v>
+        <v>3.119136064127804</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.3269569604993183</v>
+        <v>0.7784472409370002</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -722,11 +722,11 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.1039024168076811</v>
+        <v>0.1485414971899061</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Uncertain</t>
+          <t>Peripheral</t>
         </is>
       </c>
     </row>
@@ -737,7 +737,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.1507432869786511</v>
+        <v>0.1240579697670867</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.776100674682179</v>
+        <v>3.093727654334361</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -767,11 +767,11 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.2591533548442901</v>
+        <v>0.9368878724498164</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Uncertain</t>
+          <t>Peripheral</t>
         </is>
       </c>
     </row>
@@ -782,11 +782,11 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8417318074291837</v>
+        <v>0.6985246173688884</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
     </row>
@@ -797,11 +797,11 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.8698258650188675</v>
+        <v>0.248640265773091</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Uncertain</t>
         </is>
       </c>
     </row>
@@ -812,11 +812,11 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.1269581782901118</v>
+        <v>0.6863689214024996</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Uncertain</t>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -827,11 +827,11 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.5251797476040035</v>
+        <v>0.9315583583282567</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -842,11 +842,11 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.3871311160686042</v>
+        <v>0.7668635277606688</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Uncertain</t>
+          <t>Peripheral</t>
         </is>
       </c>
     </row>
@@ -857,11 +857,11 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.8155826441500762</v>
+        <v>0.4758230417541116</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.184563411566497</v>
+        <v>1.009281093850955</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -887,11 +887,11 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6818995559607646</v>
+        <v>0.9371024000914965</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -902,11 +902,11 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.5365007828069441</v>
+        <v>1.014132657646792</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -917,11 +917,11 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.8200803000737809</v>
+        <v>0.7176932556148133</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
     </row>
@@ -932,11 +932,11 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.333964837483583</v>
+        <v>0.7006581265430921</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
     </row>
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.221114250083917</v>
+        <v>0.9862130619717708</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.232531481305242</v>
+        <v>0.8830621651704349</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1.140647867850962</v>
+        <v>0.919663391682107</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1.173194594228025</v>
+        <v>0.5815057712087736</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1.225480072341521</v>
+        <v>0.8428195649858277</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.525012921856563</v>
+        <v>0.2000472989414895</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1037,11 +1037,11 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1.38430614359026</v>
+        <v>0.6540161395249384</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.6332982779884249</v>
+        <v>0.3979099273944162</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -1067,11 +1067,11 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1.373179632483779</v>
+        <v>0.08785366997304583</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Uncertain</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.8479911226519901</v>
+        <v>0.8916615251244305</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.6805663542755616</v>
+        <v>0.5502233038991322</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1112,11 +1112,11 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1.198376796304837</v>
+        <v>0.5003509396129751</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
     </row>
@@ -1127,11 +1127,11 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1.433881260945165</v>
+        <v>0.866644377864869</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
     </row>
@@ -1142,11 +1142,11 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.125829485745432</v>
+        <v>0.9221046596688497</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Uncertain</t>
+          <t>Peripheral</t>
         </is>
       </c>
     </row>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1.181524601064925</v>
+        <v>0.445703178267613</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.826332364021679</v>
+        <v>0.9122665037114662</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1.19672160165015</v>
+        <v>0.3485600061152054</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>

--- a/results/02_taxa_assemblage/MRT_Method/ModelCompar/tables/confidence_weights.xlsx
+++ b/results/02_taxa_assemblage/MRT_Method/ModelCompar/tables/confidence_weights.xlsx
@@ -516,7 +516,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -681,7 +681,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -771,7 +771,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -861,7 +861,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
     </row>
